--- a/output/pdf_financials_xlsx/PINN.xlsx
+++ b/output/pdf_financials_xlsx/PINN.xlsx
@@ -2476,19 +2476,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>9.806801999999999</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>9.820802</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>9.832701999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>9.832701999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>9.922904000000001</v>
       </c>
     </row>
     <row r="93">
@@ -4136,7 +4136,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4928,7 +4932,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>9.806801999999999</v>
       </c>

--- a/output/pdf_financials_xlsx/PINN.xlsx
+++ b/output/pdf_financials_xlsx/PINN.xlsx
@@ -1180,19 +1180,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.865416</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.272674</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.323771</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.06783699999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.14957</v>
       </c>
     </row>
     <row r="35">
@@ -1224,19 +1224,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.524069</v>
+        <v>3.389485</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.017625</v>
+        <v>0.290299</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.000825</v>
+        <v>0.324596</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.06783699999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.295829</v>
+        <v>0.445399</v>
       </c>
     </row>
     <row r="37">
@@ -1488,19 +1488,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.019265</v>
+        <v>0.153849</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.406696</v>
+        <v>0.134022</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.508235</v>
+        <v>0.184464</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.123849</v>
+        <v>0.056012</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.198069</v>
+        <v>0.048499</v>
       </c>
     </row>
     <row r="49">
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.013649</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.005989</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.013649</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.005989</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -7282,7 +7282,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>-0.013649</v>
       </c>

--- a/output/pdf_financials_xlsx/PINN.xlsx
+++ b/output/pdf_financials_xlsx/PINN.xlsx
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.01313</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.005195</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.130279</v>
+        <v>-2.117149</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.77809</v>
+        <v>-5.772895</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.05738</v>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.01313</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.005195</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -6968,7 +6968,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
         <v>0.01313</v>
       </c>
@@ -8938,7 +8942,11 @@
           <t>Depreciation of right-of-use asset (Note 3)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E139" s="5" t="n">
         <v>0.01313</v>
       </c>

--- a/output/pdf_financials_xlsx/PINN.xlsx
+++ b/output/pdf_financials_xlsx/PINN.xlsx
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-2.130279</v>
+        <v>-4.203227</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-5.77809</v>
+        <v>-5.9393</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.05738</v>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>2.072948</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>0.16121</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -2882,10 +2882,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.042446</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>0.065302</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -2976,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.000825</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -3418,10 +3418,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.042446</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.065302</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -5704,7 +5704,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -5860,7 +5864,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -6650,7 +6658,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
         <v>3.057391</v>
       </c>
@@ -7208,7 +7220,11 @@
           <t>Sale (purchase) of equipment</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -7643,7 +7659,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -9504,7 +9524,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E153" s="5" t="n">
         <v>-4.203227</v>
       </c>
@@ -9541,7 +9565,11 @@
           <t>Income from discontinued operations (Note 15)</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>2.072948</v>
       </c>
